--- a/Exam/gymtrackerpro/lib/controller/__tests__/bbt/workout-session-controller/updateWorkoutSession-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/bbt/workout-session-controller/updateWorkoutSession-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="109">
-  <si>
-    <t>Statement: workout-session-controller.updateWorkoutSession(workoutSessionId, data) – Server Action. Validates UpdateWorkoutSessionInput (optional date ISO, optional duration 0–180). Delegates to workoutSessionService.updateWorkoutSession(). Returns ActionResult&lt;WorkoutSession&gt;.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="84">
+  <si>
+    <t>Statement: updateWorkoutSession(id, data) – Validates the partial update input and returns an ActionResult&lt;WorkoutSession&gt;. Returns success with the updated session on success. An empty update object is accepted and returns the unchanged session. Returns a field-level validation error when duration or date are invalid. duration must be 0–180 (inclusive). date, when provided, must be in YYYY-MM-DD format. Returns a failure with the service error message for NotFoundError.</t>
   </si>
   <si>
     <t/>
@@ -31,27 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: workoutSessionId: string, data: UpdateWorkoutSessionInput { date?, duration?, notes? }</t>
+    <t>Input: id: string, data: UpdateWorkoutSessionInput { duration?: number, date?: string, notes?: string, ...optional }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>workoutSessionService.updateWorkoutSession is mock-injected</t>
+    <t>A known session id exists in the store. A non-existent id has no matching record. duration: 0–180 inclusive when provided. date: YYYY-MM-DD format when provided. notes: max 1024 characters when provided.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: ActionResult&lt;WorkoutSession&gt;</t>
+    <t>Output: Promise&lt;ActionResult&lt;WorkoutSession&gt;&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t xml:space="preserve">On success: updated WorkoutSession returned.
-On validation failure: errors returned.
-On AppError: message returned.</t>
+    <t>On success: session updated successfully, returned data reflects the applied changes. On validation failure: field-level validation error returned, the service is not called. On NotFoundError: operation fails with the service error message.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -66,181 +64,154 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>fields optional valid</t>
-  </si>
-  <si>
-    <t>optional duration ≤ 180 if provided</t>
+    <t>Input validity</t>
+  </si>
+  <si>
+    <t>All provided fields valid (duration: 75) → session updated successfully, returned data duration is 75</t>
+  </si>
+  <si>
+    <t>Input completeness</t>
+  </si>
+  <si>
+    <t>Empty update object {} → session updated successfully (no changes applied)</t>
+  </si>
+  <si>
+    <t>duration value</t>
+  </si>
+  <si>
+    <t>duration: -5 (below minimum) → validation fails: duration field error returned</t>
+  </si>
+  <si>
+    <t>date format</t>
+  </si>
+  <si>
+    <t>date: "2024.01.01" (invalid format) → validation fails: date field error returned</t>
+  </si>
+  <si>
+    <t>ID existence</t>
+  </si>
+  <si>
+    <t>Non-existent id (NotFoundError "Not found") → operation fails with message "Not found"</t>
+  </si>
+  <si>
+    <t>No TC</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
+    <t>Input Data</t>
+  </si>
+  <si>
+    <t>Expected</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>known existing session id, update data with duration: 75, session is updated successfully</t>
+  </si>
+  <si>
+    <t>session updated successfully, returned data duration is 75</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>known existing session id, update data: {} (empty object), session is updated successfully</t>
+  </si>
+  <si>
+    <t>session updated successfully</t>
+  </si>
+  <si>
+    <t>EC-3</t>
+  </si>
+  <si>
+    <t>known existing session id, update data with duration: -5</t>
+  </si>
+  <si>
+    <t>validation fails: duration field error returned</t>
+  </si>
+  <si>
+    <t>EC-4</t>
+  </si>
+  <si>
+    <t>known existing session id, update data with date: "2024.01.01" (invalid format)</t>
+  </si>
+  <si>
+    <t>validation fails: date field error returned</t>
+  </si>
+  <si>
+    <t>EC-5</t>
+  </si>
+  <si>
+    <t>non-existent id, valid update data, no matching record exists (NotFoundError "Not found")</t>
+  </si>
+  <si>
+    <t>operation fails with message "Not found"</t>
+  </si>
+  <si>
+    <t>Number BVA</t>
+  </si>
+  <si>
+    <t>BVA Test Case</t>
+  </si>
+  <si>
+    <t>ID length</t>
+  </si>
+  <si>
+    <t>id: "a" (length 1), a matching session record exists → session updated successfully, returned data id is "a"</t>
+  </si>
+  <si>
+    <t>id: "a" (length 1), no matching record exists (NotFoundError "Not found") → operation fails with message "Not found"</t>
   </si>
   <si>
     <t>duration range</t>
   </si>
   <si>
-    <t>duration ≤ 180</t>
-  </si>
-  <si>
-    <t>duration &gt; 180 → validation error</t>
-  </si>
-  <si>
-    <t>date format</t>
-  </si>
-  <si>
-    <t>ISO YYYY-MM-DD if provided</t>
-  </si>
-  <si>
-    <t>invalid date format → validation error</t>
-  </si>
-  <si>
-    <t>service outcome</t>
-  </si>
-  <si>
-    <t>resolves WorkoutSession</t>
-  </si>
-  <si>
-    <t>throws NotFoundError → failure</t>
-  </si>
-  <si>
-    <t>throws Error → generic failure</t>
-  </si>
-  <si>
-    <t>No TC</t>
-  </si>
-  <si>
-    <t>EC</t>
-  </si>
-  <si>
-    <t>Input Data</t>
-  </si>
-  <si>
-    <t>Expected</t>
-  </si>
-  <si>
-    <t>Actual Result</t>
-  </si>
-  <si>
-    <t>1,2,4,6</t>
-  </si>
-  <si>
-    <t>VALID_UPDATE_INPUT, service resolves WorkoutSession</t>
-  </si>
-  <si>
-    <t>{ success: true }</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>{ duration: 181 }</t>
-  </si>
-  <si>
-    <t>{ success: false, errors defined }</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>{ date: "bad-date" }</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>valid update, service throws NotFoundError</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "Session not found" }</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>valid update, service throws Error</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "An unexpected error occurred" }</t>
-  </si>
-  <si>
-    <t>Number BVA</t>
-  </si>
-  <si>
-    <t>BVA Test Case</t>
-  </si>
-  <si>
-    <t>duration boundary</t>
-  </si>
-  <si>
-    <t>duration=180 → valid</t>
-  </si>
-  <si>
-    <t>duration=181 → invalid</t>
-  </si>
-  <si>
-    <t>duration lower</t>
-  </si>
-  <si>
-    <t>duration=0 → valid</t>
-  </si>
-  <si>
-    <t>duration interior</t>
-  </si>
-  <si>
-    <t>duration=1 → valid (min+1)</t>
-  </si>
-  <si>
-    <t>duration=179 → valid (max-1)</t>
-  </si>
-  <si>
-    <t>notes length boundary</t>
-  </si>
-  <si>
-    <t>notes=1023 chars → valid (max-1)</t>
+    <t>duration: 0 (min): at minimum → session updated successfully</t>
+  </si>
+  <si>
+    <t>notes length</t>
+  </si>
+  <si>
+    <t>notes: "A".repeat(1024) (max): at maximum → session updated successfully</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>duration=180</t>
-  </si>
-  <si>
-    <t>{ duration: 180 }</t>
-  </si>
-  <si>
-    <t>schema passes</t>
-  </si>
-  <si>
-    <t>duration=181</t>
-  </si>
-  <si>
-    <t>success=false, errors.duration defined</t>
-  </si>
-  <si>
-    <t>duration=0</t>
-  </si>
-  <si>
-    <t>{ duration: 0 }</t>
-  </si>
-  <si>
-    <t>schema passes (lower boundary)</t>
-  </si>
-  <si>
-    <t>duration=1</t>
-  </si>
-  <si>
-    <t>{ duration: 1 }</t>
-  </si>
-  <si>
-    <t>success=true</t>
-  </si>
-  <si>
-    <t>duration=179</t>
-  </si>
-  <si>
-    <t>{ duration: 179 }</t>
-  </si>
-  <si>
-    <t>notes=1023</t>
-  </si>
-  <si>
-    <t>{ notes: "a".repeat(1023) }</t>
+    <t>BVA-1 (id=1, hit)</t>
+  </si>
+  <si>
+    <t>id: "a" (1 character), valid update data, a matching session record exists with id "a", session is updated successfully</t>
+  </si>
+  <si>
+    <t>session updated successfully, returned data id is "a"</t>
+  </si>
+  <si>
+    <t>BVA-2 (id=1, miss)</t>
+  </si>
+  <si>
+    <t>id: "a" (1 character), valid update data, no matching record exists (NotFoundError "Not found")</t>
+  </si>
+  <si>
+    <t>BVA-3 (dur=0)</t>
+  </si>
+  <si>
+    <t>known existing session id, update data with duration: 0, session is updated successfully</t>
+  </si>
+  <si>
+    <t>BVA-4 (notes=1024)</t>
+  </si>
+  <si>
+    <t>known existing session id, update data with notes: "A".repeat(1024), session is updated successfully</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -249,63 +220,18 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>Valid update, service resolves</t>
-  </si>
-  <si>
-    <t>success=true, session returned</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
     <t>BVA-2</t>
   </si>
   <si>
-    <t>success=false, errors defined</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
-    <t>Invalid date format</t>
-  </si>
-  <si>
-    <t>EP-4</t>
-  </si>
-  <si>
-    <t>Service throws NotFoundError</t>
-  </si>
-  <si>
-    <t>success=false, message from error</t>
-  </si>
-  <si>
-    <t>EP-5</t>
-  </si>
-  <si>
-    <t>Service throws unexpected Error</t>
-  </si>
-  <si>
-    <t>success=false, message="An unexpected error occurred"</t>
+    <t>BVA-3</t>
   </si>
   <si>
     <t>BVA-4</t>
   </si>
   <si>
-    <t>BVA-5</t>
-  </si>
-  <si>
-    <t>BVA-6</t>
-  </si>
-  <si>
-    <t>notes=1023 chars</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -336,16 +262,13 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>WSM-06</t>
+    <t>CTRL-25</t>
   </si>
   <si>
     <t>n/a</t>
   </si>
   <si>
     <t>not yet</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -861,7 +784,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -916,13 +839,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -930,13 +853,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -944,55 +867,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1015,19 +896,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1035,16 +916,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="E2" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1052,16 +933,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="E3" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1069,16 +950,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1095,7 +976,7 @@
         <v>42</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1112,7 +993,7 @@
         <v>45</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1123,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1154,11 +1035,11 @@
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+      <c r="A3" s="1">
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>50</v>
@@ -1166,7 +1047,7 @@
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>51</v>
@@ -1177,35 +1058,13 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1216,7 +1075,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1228,19 +1087,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1248,16 +1107,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1265,16 +1124,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1282,16 +1141,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1299,50 +1158,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1353,7 +1178,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1366,22 +1191,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1389,19 +1214,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1409,19 +1234,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1429,19 +1254,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1449,19 +1274,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1469,19 +1294,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1492,16 +1317,16 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1512,16 +1337,16 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1532,16 +1357,36 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>69</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1569,16 +1414,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1586,45 +1431,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>105</v>
+      <c r="A3" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="B3" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1633,19 +1478,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>108</v>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
